--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487121_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487121_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1142</v>
+        <v>3.1722</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6157</v>
+        <v>2.9147</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4985</v>
+        <v>0.2575</v>
       </c>
       <c r="G2" t="n">
         <v>2.3059</v>
@@ -610,13 +610,13 @@
         <v>0.772</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0192</v>
+        <v>-0.9228</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7998</v>
+        <v>0.0988</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-1.0216</v>
       </c>
       <c r="V2" t="n">
         <v>2.9471</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7942</v>
+        <v>2.3613</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7572</v>
+        <v>2.4582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.037</v>
+        <v>-0.0969</v>
       </c>
       <c r="G3" t="n">
         <v>1.9416</v>
@@ -688,13 +688,13 @@
         <v>0.772</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0456</v>
+        <v>0.6127</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4468</v>
+        <v>0.2542</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4924</v>
+        <v>0.3586</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ARRIAZU ARBIZU</t>
+          <t>K. ABU SHAMS SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8071</v>
+        <v>1.0734</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3254</v>
+        <v>3.2769</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5183</v>
+        <v>-2.2035</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2795</v>
+        <v>2.804</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2432</v>
+        <v>-0.1085</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5227000000000001</v>
+        <v>2.9125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4067</v>
+        <v>3.5714</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2846</v>
+        <v>0.3726</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1221</v>
+        <v>3.1988</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1272</v>
+        <v>-0.7674</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.4811</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4006</v>
+        <v>-0.2863</v>
       </c>
       <c r="P4" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07140000000000001</v>
+        <v>-1.48</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9188</v>
+        <v>-0.2945</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8474</v>
+        <v>-1.1855</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1228</v>
+        <v>-1.0226</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1228</v>
+        <v>-1.0226</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. ABU SHAMS SANCHEZ</t>
+          <t>J. ARRIAZU ARBIZU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4785</v>
+        <v>0.1458</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9765</v>
+        <v>0.8247</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.498</v>
+        <v>-0.679</v>
       </c>
       <c r="G5" t="n">
-        <v>2.804</v>
+        <v>0.2795</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1085</v>
+        <v>-0.2432</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9125</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5714</v>
+        <v>0.4067</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3726</v>
+        <v>0.2846</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1988</v>
+        <v>0.1221</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7674</v>
+        <v>-0.1272</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4811</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2863</v>
+        <v>0.4006</v>
       </c>
       <c r="P5" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.0748</v>
+        <v>-0.5899</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5949</v>
+        <v>0.4181</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.48</v>
+        <v>-1.008</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0226</v>
+        <v>-0.1228</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0226</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1866</v>
+        <v>-0.487</v>
       </c>
       <c r="E6" t="n">
-        <v>0.599</v>
+        <v>0.2986</v>
       </c>
       <c r="F6" t="n">
         <v>-0.7856</v>
@@ -922,10 +922,10 @@
         <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9796</v>
+        <v>-1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5619</v>
+        <v>0.2614</v>
       </c>
       <c r="U6" t="n">
         <v>-1.5415</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8589</v>
+        <v>-1.1444</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8566</v>
+        <v>-1.4215</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0024</v>
+        <v>0.2771</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.282</v>
+        <v>0.7554</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3166</v>
+        <v>0.3749</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9654</v>
+        <v>0.3806</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4679</v>
+        <v>-0.2129</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0776</v>
+        <v>-0.2122</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5455</v>
+        <v>-0.0007</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8141</v>
+        <v>0.9683</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3942</v>
+        <v>0.5871</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4199</v>
+        <v>0.3813</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3511</v>
+        <v>0.193</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7741</v>
+        <v>-1.3983</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5415</v>
+        <v>-0.2435</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2327</v>
+        <v>-1.1548</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6945</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6945</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8057</v>
+        <v>-1.4459</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9222</v>
+        <v>-1.6577</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1165</v>
+        <v>0.2118</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7554</v>
+        <v>-1.282</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3749</v>
+        <v>-0.3166</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3806</v>
+        <v>-0.9654</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2129</v>
+        <v>-0.4679</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2122</v>
+        <v>0.0776</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0007</v>
+        <v>-0.5455</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9683</v>
+        <v>-0.8141</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5871</v>
+        <v>-0.3942</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3813</v>
+        <v>-0.4199</v>
       </c>
       <c r="P8" t="n">
-        <v>0.193</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.0596</v>
+        <v>1.1871</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7442</v>
+        <v>0.7403</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.3154</v>
+        <v>0.4468</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6945</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8503</v>
+        <v>-1.7035</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0043</v>
+        <v>-0.804</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.846</v>
+        <v>-0.8995</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4458</v>
@@ -1156,13 +1156,13 @@
         <v>0.386</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6028</v>
+        <v>0.7496</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1468</v>
+        <v>0.347</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4561</v>
+        <v>0.4025</v>
       </c>
       <c r="V9" t="n">
         <v>0.5717</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5688</v>
+        <v>-2.8608</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1644</v>
+        <v>-1.5635</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4044</v>
+        <v>-1.2973</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4951</v>
@@ -1234,13 +1234,13 @@
         <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9386</v>
+        <v>-0.2307</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4759</v>
+        <v>0.1249</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4627</v>
+        <v>-0.3556</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3281</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2209</v>
+        <v>-4.2348</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.676</v>
+        <v>-4.4757</v>
       </c>
       <c r="F11" t="n">
-        <v>0.455</v>
+        <v>0.2409</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3585</v>
@@ -1312,13 +1312,13 @@
         <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8976</v>
+        <v>0.8837</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1018</v>
+        <v>0.3021</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7958</v>
+        <v>0.5816</v>
       </c>
       <c r="V11" t="n">
         <v>0.3281</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.216</v>
+        <v>-5.1962</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8753</v>
+        <v>-1.7751</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3408</v>
+        <v>-3.4211</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8344</v>
@@ -1390,13 +1390,13 @@
         <v>0.386</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9115</v>
+        <v>0.9313</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8144</v>
+        <v>0.9145</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0168</v>
       </c>
       <c r="V12" t="n">
         <v>-2.784</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0853</v>
+        <v>-6.2786</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.088</v>
+        <v>-5.3884</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9973</v>
+        <v>-0.8902</v>
       </c>
       <c r="G13" t="n">
         <v>-3.4587</v>
@@ -1468,13 +1468,13 @@
         <v>0.579</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0476</v>
+        <v>-0.2409</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0278</v>
+        <v>-0.2726</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.0317</v>
       </c>
       <c r="V13" t="n">
         <v>-1.228</v>
@@ -1504,7 +1504,7 @@
         <v>-16.5985</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.313000000000001</v>
+        <v>-7.3128</v>
       </c>
       <c r="F14" t="n">
         <v>-9.2858</v>
@@ -1546,13 +1546,13 @@
         <v>7.72</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.778000000000001</v>
+        <v>-1.7782</v>
       </c>
       <c r="T14" t="n">
-        <v>2.651</v>
+        <v>2.6507</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.428999999999999</v>
+        <v>-4.429</v>
       </c>
       <c r="V14" t="n">
         <v>-2.4559</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.709899999999999</v>
+        <v>7.9332</v>
       </c>
       <c r="E15" t="n">
-        <v>8.2943</v>
+        <v>6.8923</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4156</v>
+        <v>1.0409</v>
       </c>
       <c r="G15" t="n">
         <v>5.3073</v>
@@ -1624,13 +1624,13 @@
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5204</v>
+        <v>1.7437</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8172</v>
+        <v>1.4152</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7033</v>
+        <v>0.3285</v>
       </c>
       <c r="V15" t="n">
         <v>1.2682</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3944</v>
+        <v>5.0491</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0805</v>
+        <v>2.2808</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3139</v>
+        <v>2.7683</v>
       </c>
       <c r="G16" t="n">
         <v>2.4542</v>
@@ -1702,13 +1702,13 @@
         <v>2.5091</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.544</v>
+        <v>0.1107</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3081</v>
+        <v>0.5083</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8521</v>
+        <v>-0.3976</v>
       </c>
       <c r="V16" t="n">
         <v>0.9401</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MARTÍN CASTAÑEDA</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5151</v>
+        <v>2.6122</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0349</v>
+        <v>1.6967</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4801</v>
+        <v>0.9155</v>
       </c>
       <c r="G17" t="n">
-        <v>0.35</v>
+        <v>-0.9641</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1312</v>
+        <v>-1.8952</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7812</v>
+        <v>0.9311</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5035</v>
+        <v>-0.0107</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4385</v>
+        <v>-1.915</v>
       </c>
       <c r="L17" t="n">
-        <v>0.065</v>
+        <v>1.9043</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1534</v>
+        <v>-0.9534</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3073</v>
+        <v>0.0198</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8461</v>
+        <v>-0.9732</v>
       </c>
       <c r="P17" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8316</v>
+        <v>0.4412</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4965</v>
+        <v>0.2165</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3351</v>
+        <v>0.2247</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2456</v>
+        <v>2.1701</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2456</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5774</v>
+        <v>2.4499</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7954</v>
+        <v>2.3879</v>
       </c>
       <c r="F18" t="n">
-        <v>0.782</v>
+        <v>0.062</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9641</v>
+        <v>1.3521</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8952</v>
+        <v>1.0236</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9311</v>
+        <v>0.3285</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0107</v>
+        <v>0.6169</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.915</v>
+        <v>0.7968</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9043</v>
+        <v>-0.1799</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9534</v>
+        <v>0.7351</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0198</v>
+        <v>0.2268</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9732</v>
+        <v>0.5084</v>
       </c>
       <c r="P18" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5936</v>
+        <v>-0.2006</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6848</v>
+        <v>0.2572</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0912</v>
+        <v>-0.4578</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1701</v>
+        <v>-0.2456</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4559</v>
+        <v>1.5138</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2859</v>
+        <v>-1.7594</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5024</v>
+        <v>2.3354</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3865</v>
+        <v>1.2486</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1159</v>
+        <v>1.0868</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3521</v>
+        <v>2.4091</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0236</v>
+        <v>0.714</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3285</v>
+        <v>1.6951</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6169</v>
+        <v>1.6938</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7968</v>
+        <v>1.0347</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1799</v>
+        <v>0.6591</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7351</v>
+        <v>0.7153</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2268</v>
+        <v>-0.3207</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5084</v>
+        <v>1.036</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1481</v>
+        <v>-0.465</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7442</v>
+        <v>-0.0518</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4039</v>
+        <v>-0.4131</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2456</v>
+        <v>-0.5737</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5138</v>
+        <v>0.5717</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7594</v>
+        <v>-1.1454</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>A. MARTÍN CASTAÑEDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2013</v>
+        <v>2.0676</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9295</v>
+        <v>1.5342</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1308</v>
+        <v>0.5333</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2858</v>
+        <v>0.35</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.06619999999999999</v>
+        <v>1.1312</v>
       </c>
       <c r="I20" t="n">
-        <v>0.352</v>
+        <v>-0.7812</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1636</v>
+        <v>1.5035</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0726</v>
+        <v>1.4385</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.091</v>
+        <v>0.065</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4494</v>
+        <v>-1.1534</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0064</v>
+        <v>-0.3073</v>
       </c>
       <c r="O20" t="n">
-        <v>1.443</v>
+        <v>-0.8461</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1231</v>
+        <v>0.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1231</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6359</v>
+        <v>1.3841</v>
       </c>
       <c r="T20" t="n">
-        <v>0.234</v>
+        <v>0.9958</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8699</v>
+        <v>0.3883</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5717</v>
+        <v>-0.2456</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5717</v>
+        <v>-0.2456</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1929</v>
+        <v>1.9294</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7479</v>
+        <v>-0.6291</v>
       </c>
       <c r="F21" t="n">
-        <v>0.445</v>
+        <v>2.5585</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4091</v>
+        <v>0.2858</v>
       </c>
       <c r="H21" t="n">
-        <v>0.714</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6951</v>
+        <v>0.352</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6938</v>
+        <v>-1.1636</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0347</v>
+        <v>-0.0726</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6591</v>
+        <v>-1.091</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7153</v>
+        <v>1.4494</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3207</v>
+        <v>0.0064</v>
       </c>
       <c r="O21" t="n">
-        <v>1.036</v>
+        <v>1.443</v>
       </c>
       <c r="P21" t="n">
-        <v>0.965</v>
+        <v>2.1231</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9301</v>
+        <v>2.1231</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6075</v>
+        <v>0.0922</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5525</v>
+        <v>0.5345</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.055</v>
+        <v>-0.4422</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5737</v>
+        <v>-0.5717</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1454</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5788</v>
+        <v>-1.2982</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8435</v>
+        <v>-0.6432</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.655</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8399</v>
@@ -2170,13 +2170,13 @@
         <v>0.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3179</v>
+        <v>-0.0373</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.238</v>
+        <v>-0.0377</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6517</v>
+        <v>-2.1978</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9255</v>
+        <v>-2.1549</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2738</v>
+        <v>-0.0429</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7311</v>
+        <v>-1.9791</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.252</v>
+        <v>-0.8052</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5208</v>
+        <v>-1.1738</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.9316</v>
+        <v>-1.2117</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.6642</v>
+        <v>-0.5848</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7326</v>
+        <v>-0.6269</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2005</v>
+        <v>-0.7674</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5878</v>
+        <v>-0.2204</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7883</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-0</v>
+        <v>-0.193</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.965</v>
       </c>
       <c r="R23" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0794</v>
+        <v>0.2601</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9711</v>
+        <v>0.0218</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8917</v>
+        <v>0.2383</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2643</v>
+        <v>-2.9469</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3552</v>
+        <v>-3.3275</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.3806</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9791</v>
+        <v>-2.7311</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8052</v>
+        <v>-4.252</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1738</v>
+        <v>1.5208</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2117</v>
+        <v>-2.9316</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5848</v>
+        <v>-3.6642</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6269</v>
+        <v>0.7326</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7674</v>
+        <v>0.2005</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2204</v>
+        <v>-0.5878</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5469000000000001</v>
+        <v>0.7883</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.965</v>
       </c>
       <c r="R24" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1937</v>
+        <v>-0.2158</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1785</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3721</v>
+        <v>-0.7849</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,34 +2359,34 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>16.5986</v>
+        <v>17.9339</v>
       </c>
       <c r="E25" t="n">
         <v>9.2858</v>
       </c>
       <c r="F25" t="n">
-        <v>7.3126</v>
+        <v>8.648</v>
       </c>
       <c r="G25" t="n">
-        <v>4.6443</v>
+        <v>4.644299999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03529999999999955</v>
+        <v>0.03529999999999944</v>
       </c>
       <c r="I25" t="n">
         <v>4.609</v>
       </c>
       <c r="J25" t="n">
-        <v>5.336200000000002</v>
+        <v>5.3362</v>
       </c>
       <c r="K25" t="n">
         <v>1.1054</v>
       </c>
       <c r="L25" t="n">
-        <v>4.230700000000001</v>
+        <v>4.2307</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6919999999999997</v>
+        <v>-0.6919999999999998</v>
       </c>
       <c r="N25" t="n">
         <v>-1.0702</v>
@@ -2395,7 +2395,7 @@
         <v>0.3785000000000002</v>
       </c>
       <c r="P25" t="n">
-        <v>7.7203</v>
+        <v>7.720300000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-7.7201</v>
@@ -2404,13 +2404,13 @@
         <v>15.4407</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7781</v>
+        <v>3.1133</v>
       </c>
       <c r="T25" t="n">
-        <v>4.428900000000001</v>
+        <v>4.4289</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.6509</v>
+        <v>-1.3155</v>
       </c>
       <c r="V25" t="n">
         <v>2.4559</v>
